--- a/outputs/Residencial_Exemplo_202604_seens.xlsx
+++ b/outputs/Residencial_Exemplo_202604_seens.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,13 +51,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,122 +440,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:L20"/>
+  <dimension ref="A5:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="5"/>
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Residencial Exemplo</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL EXEMPLO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Balancete mensal</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BALANCETE MENSAL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Competência abril de 2026</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>COMPETÊNCIA ABRIL DE 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>(+) RECEITAS — Taxas</t>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>(+) RECEITAS MENSAIS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Taxa condominial</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="n">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TAXA CONDOMINIAL</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Multas e juros</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>120.5</v>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DIVERSAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>SALÁRIOS</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="L14" s="1" t="n">
-        <v>15120.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>(-) DESPESAS — Pessoal</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Salários</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="n">
+      <c r="L16" s="4" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="n">
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL RECEITAS DO MÊS</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL DESPESAS DO MÊS</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
         <v>8000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>(-) DESPESAS — Manutenção</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Elevadores</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>450</v>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>RESUMO DO MÊS</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="n">
-        <v>450</v>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DESPESAS</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (RECEITAS - DESPESAS)</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>7000</v>
       </c>
     </row>
   </sheetData>
